--- a/doc/怪物列表.xlsx
+++ b/doc/怪物列表.xlsx
@@ -361,7 +361,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -575,7 +575,91 @@
         <v>1.0</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>10015</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>青石村野外</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>野鸡</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>鸡肉 (回3血);修为+5~8</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>10016</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>青石村野外</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>稻草人</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>木桩僵硬，几乎不会闪避</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>草芯束;修为+8~12</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <drawing ns1:id="rId1"/>
 </worksheet>
 </file>